--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LE6R\Downloads\concert-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A572363-0D29-49BC-AAB5-6AD477268D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6178CE-401B-4AEF-A9C9-B7B86E98E5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,9 +132,6 @@
     <t>Def Leppard</t>
   </si>
   <si>
-    <t>The Colosseum</t>
-  </si>
-  <si>
     <t>Sammy Hagar</t>
   </si>
   <si>
@@ -208,6 +205,9 @@
   </si>
   <si>
     <t>Ticket vendor for event is AXS not Ticketmaster</t>
+  </si>
+  <si>
+    <t>The Colosseum at Caesars Palace</t>
   </si>
 </sst>
 </file>
@@ -721,7 +721,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
@@ -762,10 +762,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>19</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>16</v>
@@ -928,10 +928,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>16</v>
@@ -962,13 +962,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>16</v>
@@ -1132,13 +1132,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>16</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>16</v>
@@ -1231,15 +1231,15 @@
       <c r="L15" s="10"/>
       <c r="M15" s="11"/>
       <c r="N15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>16</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>19</v>

--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LE6R\Downloads\concert-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6178CE-401B-4AEF-A9C9-B7B86E98E5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF85E0F3-28BD-4754-9760-D645A33DBD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1098,16 +1098,16 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E12" s="4">
         <v>46288</v>
@@ -1119,11 +1119,11 @@
         <v>46295</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="9">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="10"/>
@@ -1132,19 +1132,19 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="4">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="F13" s="4">
         <v>46266</v>
@@ -1153,11 +1153,11 @@
         <v>46295</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="9">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="10"/>
@@ -1704,8 +1704,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N42">
-    <sortCondition ref="E2:E42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
+    <sortCondition ref="E2:E17"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LE6R\Downloads\concert-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF85E0F3-28BD-4754-9760-D645A33DBD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8039A765-D40B-4487-9744-F63222FDCBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="57">
   <si>
     <t>Artist</t>
   </si>
@@ -917,13 +917,23 @@
       <c r="H6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="J6" s="9">
         <v>120</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="11"/>
+      <c r="K6" s="5">
+        <v>70</v>
+      </c>
+      <c r="L6" s="10">
+        <f>IF(AND(K6&lt;&gt;"",J6&lt;&gt;""),K6-J6,"")</f>
+        <v>-50</v>
+      </c>
+      <c r="M6" s="11">
+        <f>IF(AND(K6&lt;&gt;"",J6&lt;&gt;""),(K6-J6)/J6,"")</f>
+        <v>-0.41666666666666669</v>
+      </c>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -951,13 +961,23 @@
       <c r="H7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="8"/>
+      <c r="I7" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="J7" s="9">
         <v>65</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
+      <c r="K7" s="5">
+        <v>74</v>
+      </c>
+      <c r="L7" s="10">
+        <f>IF(AND(K7&lt;&gt;"",J7&lt;&gt;""),K7-J7,"")</f>
+        <v>9</v>
+      </c>
+      <c r="M7" s="11">
+        <f>IF(AND(K7&lt;&gt;"",J7&lt;&gt;""),(K7-J7)/J7,"")</f>
+        <v>0.13846153846153847</v>
+      </c>
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">

--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LE6R\Downloads\concert-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8039A765-D40B-4487-9744-F63222FDCBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07A6D86-BEBB-4DCC-9A06-B7D727CE4DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="56">
   <si>
     <t>Artist</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>Marilyn Manson</t>
-  </si>
-  <si>
-    <t>Motley Crue</t>
   </si>
   <si>
     <t>Five Finger Death Punch</t>
@@ -657,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -721,7 +718,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
@@ -751,11 +748,11 @@
         <v>130</v>
       </c>
       <c r="L2" s="10">
-        <f>IF(AND(K2&lt;&gt;"",J2&lt;&gt;""),K2-J2,"")</f>
+        <f t="shared" ref="L2:L9" si="0">IF(AND(K2&lt;&gt;"",J2&lt;&gt;""),K2-J2,"")</f>
         <v>-50</v>
       </c>
       <c r="M2" s="11">
-        <f>IF(AND(K2&lt;&gt;"",J2&lt;&gt;""),(K2-J2)/J2,"")</f>
+        <f t="shared" ref="M2:M9" si="1">IF(AND(K2&lt;&gt;"",J2&lt;&gt;""),(K2-J2)/J2,"")</f>
         <v>-0.27777777777777779</v>
       </c>
       <c r="N2" s="3"/>
@@ -795,11 +792,11 @@
         <v>180</v>
       </c>
       <c r="L3" s="10">
-        <f>IF(AND(K3&lt;&gt;"",J3&lt;&gt;""),K3-J3,"")</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="M3" s="11">
-        <f>IF(AND(K3&lt;&gt;"",J3&lt;&gt;""),(K3-J3)/J3,"")</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="N3" s="3"/>
@@ -839,11 +836,11 @@
         <v>200</v>
       </c>
       <c r="L4" s="10">
-        <f>IF(AND(K4&lt;&gt;"",J4&lt;&gt;""),K4-J4,"")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M4" s="11">
-        <f>IF(AND(K4&lt;&gt;"",J4&lt;&gt;""),(K4-J4)/J4,"")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N4" s="3"/>
@@ -883,11 +880,11 @@
         <v>270</v>
       </c>
       <c r="L5" s="10">
-        <f>IF(AND(K5&lt;&gt;"",J5&lt;&gt;""),K5-J5,"")</f>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="M5" s="11">
-        <f>IF(AND(K5&lt;&gt;"",J5&lt;&gt;""),(K5-J5)/J5,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
       <c r="N5" s="3"/>
@@ -897,7 +894,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>16</v>
@@ -927,11 +924,11 @@
         <v>70</v>
       </c>
       <c r="L6" s="10">
-        <f>IF(AND(K6&lt;&gt;"",J6&lt;&gt;""),K6-J6,"")</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="M6" s="11">
-        <f>IF(AND(K6&lt;&gt;"",J6&lt;&gt;""),(K6-J6)/J6,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.41666666666666669</v>
       </c>
       <c r="N6" s="3"/>
@@ -941,7 +938,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>16</v>
@@ -971,11 +968,11 @@
         <v>74</v>
       </c>
       <c r="L7" s="10">
-        <f>IF(AND(K7&lt;&gt;"",J7&lt;&gt;""),K7-J7,"")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="M7" s="11">
-        <f>IF(AND(K7&lt;&gt;"",J7&lt;&gt;""),(K7-J7)/J7,"")</f>
+        <f t="shared" si="1"/>
         <v>0.13846153846153847</v>
       </c>
       <c r="N7" s="3"/>
@@ -985,10 +982,10 @@
         <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -1005,18 +1002,28 @@
       <c r="H8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="8"/>
+      <c r="I8" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="J8" s="9">
         <v>170</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="11"/>
+      <c r="K8" s="5">
+        <v>219</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" si="1"/>
+        <v>0.28823529411764703</v>
+      </c>
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
@@ -1039,21 +1046,31 @@
       <c r="H9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="8"/>
+      <c r="I9" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="J9" s="9">
         <v>120</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="11"/>
+      <c r="K9" s="5">
+        <v>50</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="0"/>
+        <v>-70</v>
+      </c>
+      <c r="M9" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.58333333333333337</v>
+      </c>
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1071,7 +1088,7 @@
         <v>46295</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="9">
@@ -1087,10 +1104,10 @@
         <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
@@ -1118,16 +1135,16 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="4">
         <v>46288</v>
@@ -1139,11 +1156,11 @@
         <v>46295</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="9">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="10"/>
@@ -1152,10 +1169,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>16</v>
@@ -1164,20 +1181,20 @@
         <v>17</v>
       </c>
       <c r="E13" s="4">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="F13" s="4">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="G13" s="4">
-        <v>46295</v>
+        <v>46325</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="9">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="10"/>
@@ -1189,7 +1206,7 @@
         <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>16</v>
@@ -1198,7 +1215,7 @@
         <v>17</v>
       </c>
       <c r="E14" s="4">
-        <v>46298</v>
+        <v>46318</v>
       </c>
       <c r="F14" s="4">
         <v>46296</v>
@@ -1211,19 +1228,21 @@
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="9">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="10"/>
       <c r="M14" s="11"/>
-      <c r="N14" s="3"/>
+      <c r="N14" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>16</v>
@@ -1232,34 +1251,32 @@
         <v>17</v>
       </c>
       <c r="E15" s="4">
-        <v>46318</v>
+        <v>46360</v>
       </c>
       <c r="F15" s="4">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="G15" s="4">
-        <v>46325</v>
+        <v>46387</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="9">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="10"/>
       <c r="M15" s="11"/>
-      <c r="N15" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="N15" s="3"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>16</v>
@@ -1268,7 +1285,7 @@
         <v>17</v>
       </c>
       <c r="E16" s="4">
-        <v>46360</v>
+        <v>46367</v>
       </c>
       <c r="F16" s="4">
         <v>46357</v>
@@ -1277,11 +1294,11 @@
         <v>46387</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="9">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="10"/>
@@ -1289,34 +1306,16 @@
       <c r="N16" s="3"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="4">
-        <v>46367</v>
-      </c>
-      <c r="F17" s="4">
-        <v>46357</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46387</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="7"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="9">
-        <v>130</v>
-      </c>
+      <c r="J17" s="9"/>
       <c r="K17" s="5"/>
       <c r="L17" s="10"/>
       <c r="M17" s="11"/>
@@ -1706,26 +1705,10 @@
       <c r="M41" s="11"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="3"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
-    <sortCondition ref="E2:E17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N16">
+    <sortCondition ref="E2:E16"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LE6R\Downloads\concert-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07A6D86-BEBB-4DCC-9A06-B7D727CE4DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F34E8EF-EEA6-4B3C-B932-86AEB6C7A86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1184,10 +1184,10 @@
         <v>46289</v>
       </c>
       <c r="F13" s="4">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="G13" s="4">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>15</v>
@@ -1221,7 +1221,7 @@
         <v>46296</v>
       </c>
       <c r="G14" s="4">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>15</v>

--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LE6R\Downloads\concert-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F34E8EF-EEA6-4B3C-B932-86AEB6C7A86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23920260-FECB-40B3-8399-677993C04377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1187,7 +1187,7 @@
         <v>46266</v>
       </c>
       <c r="G13" s="4">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>15</v>
